--- a/CDRLGEX.xlsx
+++ b/CDRLGEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevingransee/Desktop/econ_msc/MC-CDR_Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BB4F2E-AB14-0545-AA38-F71C6E5FBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D2626A-D392-A84F-BE72-18BFAEEFF09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36440" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{AF13AD6E-D5B1-475E-858A-F20B88DBFF16}"/>
   </bookViews>
@@ -514,7 +514,7 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -526,7 +526,7 @@
         <v>0.1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -540,7 +540,7 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -552,7 +552,7 @@
         <v>0.25</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -566,7 +566,7 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -578,7 +578,7 @@
         <v>0.05</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -592,7 +592,7 @@
         <v>70</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0.4</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -618,7 +618,7 @@
         <v>50</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>0.15</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -644,7 +644,7 @@
         <v>45</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -656,7 +656,7 @@
         <v>0.12</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -670,7 +670,7 @@
         <v>80</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -696,7 +696,7 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>0.3</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -722,7 +722,7 @@
         <v>60</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0.22</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -748,7 +748,7 @@
         <v>42</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>0.18</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -774,7 +774,7 @@
         <v>65</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0.35</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -800,7 +800,7 @@
         <v>38</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0.99</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
